--- a/templates/contracts/Akt_hygiene.xlsx
+++ b/templates/contracts/Akt_hygiene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\templates\contracts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B82DFF9-FCC7-4D97-9986-2AA2A0D4D34B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD7BA6D-84E5-4095-9223-C09C0A0C99F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="285" windowWidth="26730" windowHeight="20715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Акт</t>
   </si>
@@ -85,12 +85,6 @@
   </si>
   <si>
     <t>{{DATE_END}}</t>
-  </si>
-  <si>
-    <t>Делаем для формирования новый документ "Акт об обеспечении круглосуточного питьевого режима ".  Формировать будем по привычке в ексель. У меня есть готовый шаблон Akt_water.xlsx, который находится в папке templates\contracts. Ниже опишу что нужно. Так как файл почти идентичен гигиене, может имеет смысл чтобы не плодить лишние файлы и не дублировать сделать это всё не отдельно? или как ты считаешь лучше сделать?
-1. Шаблон почти идентичен Akt_hygiene.xlsx, теги используются теже что и там, почти ВСЁ идентично, за одни исключением. В гигиене мы перечисляем в теге {{SCHOOL_HEADER}} сверху школу и руководителя, а в этом докумнете мне нужен тег, просто для перечисления школ, по формату : ГБОУ Школа №2054; ГБОУ Школа №37; ГБОУ Школа №384;    ГБОУ Школа №554; ГБОУ Школа №1249; ГБОУ Школа №1272; ГБОУ Школа №904; ГБОУ Школа №1476 (тоесть через точку запятую с пробелом. все школы должны писаться жирным
-2. нужна кнопка для формирования в документах, с выборам только сборов
-Выдай полные файлы для замены</t>
   </si>
 </sst>
 </file>
@@ -472,13 +466,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="N7" s="7"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
